--- a/assessment_forms/031_student_social_skills_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/031_student_social_skills_assessment_form--assessment_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,13 +515,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Student's Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,18 +533,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>staff_member</t>
+          <t>student_grade_level</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Staff Member</t>
+          <t>Grade Level</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,18 +556,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>teacher_feedback_1</t>
+          <t>student_age</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What were your observations?</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>teacher_feedback_2</t>
+          <t>teacher_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What were your actions?</t>
+          <t>Teacher's Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teacher_feedback_3</t>
+          <t>teacher_feedback_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What do you think the student will need?</t>
+          <t>What were your observations?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>teacher_feedback_4</t>
+          <t>teacher_feedback_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What do you think the student will be able to accomplish in the next 6 months?</t>
+          <t>What are some specific strengths you've noticed?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,18 +648,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>teacher_feedback_5</t>
+          <t>teacher_feedback_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What are some strategies to help the student develop these skills further?</t>
+          <t>What areas do you think the student needs improvement in?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -676,13 +676,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What were your observations?</t>
+          <t>Staff Feedback 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -699,13 +699,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What were your actions?</t>
+          <t>Staff Feedback 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -722,13 +722,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What do you think the student will need?</t>
+          <t>Staff Feedback 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What do you think the student will be able to accomplish in the next 6 months?</t>
+          <t>What support strategies have you found effective?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>staff_feedback_5</t>
+          <t>teacher_support_strategies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -774,7 +774,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
